--- a/ig/test-tabs-svs/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
+++ b/ig/test-tabs-svs/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="629">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1563,12 +1563,6 @@
     <t>Centre Périnatal de Proximité (CPP)</t>
   </si>
   <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Equipes Mobiles de Soins Palliatifs (EMSP)</t>
-  </si>
-  <si>
     <t>253</t>
   </si>
   <si>
@@ -1627,24 +1621,6 @@
   </si>
   <si>
     <t>Unité de soins intensifs spécialisés hématologie (USIH)</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Equipe mobile d'algologie</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Equipe mobile de gériatrie (EMG)</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Equipe mobile d'endocrinologie, diabétologie, métabolisme et nutrition</t>
   </si>
   <si>
     <t>268</t>
@@ -2185,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B306"/>
+  <dimension ref="A1:B302"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4597,47 +4573,15 @@
         <v>626</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B302" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="B302" t="s" s="2">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B303" t="s" s="2">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B304" t="s" s="2">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B305" t="s" s="2">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B306" t="s" s="2">
-        <v>636</v>
       </c>
     </row>
   </sheetData>
